--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513647_FASEFINALAFFA1_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513647_FASEFINALAFFA1_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7457</v>
+        <v>3.0603</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8414</v>
+        <v>4.0514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9043</v>
+        <v>-0.991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1229</v>
+        <v>-0.6916</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7713</v>
+        <v>-0.6481</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6484</v>
+        <v>-0.0435</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7754</v>
+        <v>0.728</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2778</v>
+        <v>0.7518</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5024</v>
+        <v>-0.0238</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6526</v>
+        <v>-1.4196</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5065</v>
+        <v>-1.4</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.146</v>
+        <v>-0.0197</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7789</v>
+        <v>1.7526</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9737</v>
+        <v>-0.3895</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7526</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1234</v>
+        <v>-0.4428</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0397</v>
+        <v>-0.2298</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0837</v>
+        <v>-0.213</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2795</v>
+        <v>2.4421</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.9426</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2795</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4832</v>
+        <v>1.528</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1681</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.8208</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6916</v>
+        <v>0.1229</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6481</v>
+        <v>0.7713</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0435</v>
+        <v>-0.6484</v>
       </c>
       <c r="J3" t="n">
-        <v>0.728</v>
+        <v>0.7754</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7518</v>
+        <v>1.2778</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0238</v>
+        <v>-0.5024</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4196</v>
+        <v>-0.6526</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4</v>
+        <v>-0.5065</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0197</v>
+        <v>-0.146</v>
       </c>
       <c r="P3" t="n">
+        <v>0.7789</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.9737</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.7526</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.3895</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.1421</v>
-      </c>
       <c r="S3" t="n">
-        <v>-1.0199</v>
+        <v>0.9056</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.113</v>
+        <v>0.9054</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0931</v>
+        <v>0.0002</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4421</v>
+        <v>-0.2795</v>
       </c>
       <c r="W3" t="n">
-        <v>3.9426</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5005</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1791</v>
+        <v>0.8083</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2382</v>
+        <v>0.8395</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0591</v>
+        <v>-0.0313</v>
       </c>
       <c r="G4" t="n">
         <v>0.425</v>
@@ -766,13 +766,13 @@
         <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5594</v>
+        <v>0.1885</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.1421</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0186</v>
+        <v>0.0464</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0313</v>
+        <v>-0.386</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6047</v>
+        <v>-0.9038</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5734</v>
+        <v>0.5177</v>
       </c>
       <c r="G6" t="n">
         <v>-1.039</v>
@@ -922,13 +922,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4234</v>
+        <v>0.0688</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3553</v>
+        <v>0.0563</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0125</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9704</v>
+        <v>-1.0778</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1941</v>
+        <v>-0.2457</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7764</v>
+        <v>-0.832</v>
       </c>
       <c r="G8" t="n">
         <v>0.1203</v>
@@ -1078,13 +1078,13 @@
         <v>2.1421</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0787</v>
+        <v>0.9714</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7661</v>
+        <v>0.7144</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3127</v>
+        <v>0.257</v>
       </c>
       <c r="V8" t="n">
         <v>-1.78</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4905</v>
+        <v>-1.7392</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0387</v>
+        <v>-3.2899</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5482</v>
+        <v>1.5508</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3019</v>
+        <v>2.8385</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2125</v>
+        <v>0.5285</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0895</v>
+        <v>2.31</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6599</v>
+        <v>2.7304</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6599</v>
+        <v>0.7929</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9375</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.642</v>
+        <v>0.1081</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4474</v>
+        <v>-0.2644</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0895</v>
+        <v>0.3725</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1947</v>
+        <v>-6.2316</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3632</v>
+        <v>-7.9842</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1684</v>
+        <v>1.7526</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0062</v>
+        <v>0.4328</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0157</v>
+        <v>0.4633</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0219</v>
+        <v>-0.0305</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5545</v>
+        <v>-2.4503</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0281</v>
+        <v>-2.9151</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5264</v>
+        <v>0.4648</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4597</v>
+        <v>-2.3019</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9782</v>
+        <v>-1.2125</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4816</v>
+        <v>-1.0895</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0032</v>
+        <v>-1.6599</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2059</v>
+        <v>-1.6599</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2026</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4565</v>
+        <v>-0.642</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7723</v>
+        <v>0.4474</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6842</v>
+        <v>-1.0895</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1947</v>
+        <v>-1.3632</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7789</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4389</v>
+        <v>0.0464</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1698</v>
+        <v>0.108</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2691</v>
+        <v>-0.0616</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1179</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2816</v>
+        <v>-2.5661</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6097</v>
+        <v>-0.9285</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3281</v>
+        <v>-1.6377</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8385</v>
+        <v>-2.4597</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5285</v>
+        <v>-1.9782</v>
       </c>
       <c r="I11" t="n">
-        <v>2.31</v>
+        <v>-0.4816</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7304</v>
+        <v>-1.0032</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7929</v>
+        <v>-1.2059</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9375</v>
+        <v>0.2026</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1081</v>
+        <v>-1.4565</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2644</v>
+        <v>-0.7723</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3725</v>
+        <v>-0.6842</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.2316</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.9842</v>
+        <v>-0.1947</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7526</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1095</v>
+        <v>0.4273</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8565</v>
+        <v>0.2695</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2531</v>
+        <v>0.1578</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2211</v>
+        <v>-1.1179</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5005</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2795</v>
+        <v>-1.1179</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4259</v>
+        <v>-3.2628</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2247</v>
+        <v>-2.2007</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2012</v>
+        <v>-1.0621</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8258</v>
@@ -1390,13 +1390,13 @@
         <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2164</v>
+        <v>-0.0533</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0683</v>
+        <v>-0.0443</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1481</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1626</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CANAS</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0852</v>
+        <v>-5.0212</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8424</v>
+        <v>-4.2778</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2428</v>
+        <v>-0.7435</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8753</v>
+        <v>-1.6479</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.538</v>
+        <v>-1.5645</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3373</v>
+        <v>-0.0834</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1465</v>
+        <v>-0.3665</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.5631</v>
+        <v>-0.708</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5835</v>
+        <v>0.3416</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2712</v>
+        <v>-1.2815</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0251</v>
+        <v>-0.8565</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2461</v>
+        <v>-0.4249</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3895</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1684</v>
+        <v>-3.5053</v>
       </c>
       <c r="R13" t="n">
         <v>1.5579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4018</v>
+        <v>-0.2049</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4726</v>
+        <v>-0.4061</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0708</v>
+        <v>0.2012</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.0011</v>
+        <v>-1.2211</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.0011</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>D. FERNANDEZ CANAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.0652</v>
+        <v>-5.153</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.0992</v>
+        <v>-3.9937</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9661</v>
+        <v>-1.1593</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6479</v>
+        <v>-2.8753</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5645</v>
+        <v>-2.538</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0834</v>
+        <v>-0.3373</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3665</v>
+        <v>-3.1465</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.708</v>
+        <v>-2.5631</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3416</v>
+        <v>-0.5835</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2815</v>
+        <v>0.2712</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8565</v>
+        <v>0.0251</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4249</v>
+        <v>0.2461</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.9474</v>
+        <v>0.3895</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.5053</v>
+        <v>-1.1684</v>
       </c>
       <c r="R14" t="n">
         <v>1.5579</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2489</v>
+        <v>0.3339</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2275</v>
+        <v>0.3212</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0214</v>
+        <v>0.0127</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2211</v>
+        <v>-3.0011</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2211</v>
+        <v>-3.0011</v>
       </c>
     </row>
     <row r="15">
@@ -1579,28 +1579,28 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.7479</v>
+        <v>-16.5111</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.0347</v>
+        <v>-12.7979</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.7135</v>
+        <v>-3.7133</v>
       </c>
       <c r="G15" t="n">
         <v>-9.3292</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.3687</v>
+        <v>-7.368699999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.960699999999999</v>
+        <v>-1.9607</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.3173</v>
+        <v>-1.317300000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.908799999999999</v>
+        <v>-2.9088</v>
       </c>
       <c r="L15" t="n">
         <v>1.5913</v>
@@ -1612,25 +1612,25 @@
         <v>-4.46</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.552299999999999</v>
+        <v>-3.5523</v>
       </c>
       <c r="P15" t="n">
         <v>-3.8949</v>
       </c>
       <c r="Q15" t="n">
-        <v>-18.5</v>
+        <v>-18.49999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>14.6051</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3753</v>
+        <v>2.6119</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0015</v>
+        <v>2.2382</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3738</v>
+        <v>0.3737</v>
       </c>
       <c r="V15" t="n">
         <v>-5.899</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.143800000000001</v>
+        <v>8.123799999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7988</v>
+        <v>6.0014</v>
       </c>
       <c r="F16" t="n">
-        <v>2.345</v>
+        <v>2.1224</v>
       </c>
       <c r="G16" t="n">
         <v>1.833</v>
@@ -1702,13 +1702,13 @@
         <v>1.3632</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1081</v>
+        <v>1.0881</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2515</v>
+        <v>0.4541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8566</v>
+        <v>0.634</v>
       </c>
       <c r="V16" t="n">
         <v>3.8395</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5664</v>
+        <v>4.1258</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0614</v>
+        <v>-0.6627</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6278</v>
+        <v>4.7885</v>
       </c>
       <c r="G17" t="n">
         <v>4.0224</v>
@@ -1780,13 +1780,13 @@
         <v>2.3368</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.125</v>
+        <v>-0.5655</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9275</v>
+        <v>-0.5288</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1974</v>
+        <v>-0.0367</v>
       </c>
       <c r="V17" t="n">
         <v>0.2795</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3276</v>
+        <v>2.6153</v>
       </c>
       <c r="E18" t="n">
-        <v>2.362</v>
+        <v>-0.3321</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9656</v>
+        <v>2.9474</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8687</v>
+        <v>1.6508</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5121</v>
+        <v>1.7611</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3809</v>
+        <v>-0.1103</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.484</v>
+        <v>1.1086</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2135</v>
+        <v>1.0597</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7295</v>
+        <v>0.0489</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3528</v>
+        <v>0.5423</v>
       </c>
       <c r="N18" t="n">
         <v>0.7014</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6514</v>
+        <v>-0.1591</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1421</v>
+        <v>1.7526</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1421</v>
+        <v>2.7263</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9273</v>
+        <v>-0.7882</v>
       </c>
       <c r="T18" t="n">
-        <v>1.066</v>
+        <v>-0.467</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1387</v>
+        <v>-0.3212</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1316</v>
+        <v>2.2806</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1316</v>
+        <v>1.2655</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1316</v>
+        <v>0.8687</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3079</v>
+        <v>-0.5121</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8237</v>
+        <v>1.3809</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1316</v>
+        <v>-0.484</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3079</v>
+        <v>-1.2135</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8237</v>
+        <v>0.7295</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.3528</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.7014</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.6514</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.1198</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0304</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.0893</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0837</v>
+        <v>2.1316</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7308</v>
+        <v>2.1316</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8145</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6508</v>
+        <v>2.1316</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7611</v>
+        <v>0.3079</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1103</v>
+        <v>1.8237</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1086</v>
+        <v>2.1316</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0597</v>
+        <v>0.3079</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0489</v>
+        <v>1.8237</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5423</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7014</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1591</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7526</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7263</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3198</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8657</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4541</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3314</v>
+        <v>1.081</v>
       </c>
       <c r="E21" t="n">
         <v>0.1016</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2298</v>
+        <v>0.9794</v>
       </c>
       <c r="G21" t="n">
         <v>0.3372</v>
@@ -2092,13 +2092,13 @@
         <v>0.7789</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2474</v>
+        <v>-0.003</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2473</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4948</v>
+        <v>0.2443</v>
       </c>
       <c r="V21" t="n">
         <v>0.9416</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4193</v>
+        <v>1.0798</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2716</v>
+        <v>1.2023</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6909</v>
+        <v>-0.1226</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1742</v>
+        <v>-0.6813</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8872</v>
+        <v>0.9237</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0614</v>
+        <v>-1.605</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3467</v>
+        <v>0.4804</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4516</v>
+        <v>0.9828</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1049</v>
+        <v>-0.5024</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.521</v>
+        <v>-1.1617</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4356</v>
+        <v>-0.0591</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9565</v>
+        <v>-1.1026</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9737</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9737</v>
+        <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3802</v>
+        <v>0.4026</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6183</v>
+        <v>0.0314</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2382</v>
+        <v>0.3712</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.7216</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.6116</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1549</v>
+        <v>1.0452</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3053</v>
+        <v>0.3264</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1504</v>
+        <v>0.7187</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6813</v>
+        <v>-0.1742</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9237</v>
+        <v>0.8872</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.605</v>
+        <v>-1.0614</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4804</v>
+        <v>0.3467</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9828</v>
+        <v>0.4516</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5024</v>
+        <v>-0.1049</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1617</v>
+        <v>-0.521</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0591</v>
+        <v>0.4356</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1026</v>
+        <v>-0.9565</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3632</v>
+        <v>0.9737</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5579</v>
+        <v>0.9737</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5223</v>
+        <v>0.2457</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8657</v>
+        <v>-0.0203</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3434</v>
+        <v>0.266</v>
       </c>
       <c r="V23" t="n">
-        <v>2.7216</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.6116</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2716</v>
+        <v>-0.1432</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3528</v>
+        <v>-2.5521</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0812</v>
+        <v>2.4089</v>
       </c>
       <c r="G24" t="n">
         <v>0.6156</v>
@@ -2326,13 +2326,13 @@
         <v>2.5316</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4977</v>
+        <v>-0.3694</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2778</v>
+        <v>0.0785</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7755</v>
+        <v>-0.4479</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4712</v>
+        <v>-1.1503</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6046</v>
+        <v>-3.0579</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0758</v>
+        <v>1.9076</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5618</v>
+        <v>0.8195</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9442</v>
+        <v>-1.2295</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.506</v>
+        <v>2.049</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3302</v>
+        <v>-0.6057</v>
       </c>
       <c r="K25" t="n">
-        <v>1.8731</v>
+        <v>-1.8704</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5429</v>
+        <v>1.2647</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.892</v>
+        <v>1.4251</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9288999999999999</v>
+        <v>0.6409</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9631</v>
+        <v>0.7843</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.7526</v>
+        <v>0.1947</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.921</v>
+        <v>-1.9474</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1684</v>
+        <v>2.1421</v>
       </c>
       <c r="S25" t="n">
-        <v>1.5638</v>
+        <v>-0.9435</v>
       </c>
       <c r="T25" t="n">
-        <v>1.916</v>
+        <v>-0.5048</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3522</v>
+        <v>-0.4386</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2795</v>
+        <v>-1.2211</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.5544</v>
+        <v>-1.3207</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.3569</v>
+        <v>-0.219</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8025</v>
+        <v>-1.1016</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8195</v>
+        <v>-1.5321</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.2295</v>
+        <v>-1.7329</v>
       </c>
       <c r="I26" t="n">
-        <v>2.049</v>
+        <v>0.2008</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6057</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.8704</v>
+        <v>-1.2264</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2647</v>
+        <v>1.2968</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4251</v>
+        <v>-1.6025</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6409</v>
+        <v>-0.5065</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7843</v>
+        <v>-1.096</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1947</v>
+        <v>0.7789</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1421</v>
+        <v>0.7789</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3476</v>
+        <v>-0.2365</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8038999999999999</v>
+        <v>0.0415</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5437</v>
+        <v>-0.278</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2211</v>
+        <v>-0.3311</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,64 +2515,64 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.1135</v>
+        <v>-1.4563</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8171</v>
+        <v>-0.4918</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2964</v>
+        <v>-0.9645</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.5321</v>
+        <v>-0.5618</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.7329</v>
+        <v>0.9442</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2008</v>
+        <v>-1.506</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07049999999999999</v>
+        <v>1.3302</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.2264</v>
+        <v>1.8731</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2968</v>
+        <v>-0.5429</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.6025</v>
+        <v>-1.892</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.5065</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.096</v>
+        <v>-0.9631</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7789</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R27" t="n">
-        <v>0.7789</v>
+        <v>1.1684</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0293</v>
+        <v>0.5787</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5565</v>
+        <v>0.8196</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4728</v>
+        <v>-0.2409</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3311</v>
+        <v>0.2795</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.3311</v>
+        <v>0.2795</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>17.748</v>
+        <v>18.4126</v>
       </c>
       <c r="E28" t="n">
-        <v>3.713300000000002</v>
+        <v>3.713199999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>14.0347</v>
+        <v>14.6992</v>
       </c>
       <c r="G28" t="n">
         <v>9.329400000000001</v>
@@ -2623,7 +2623,7 @@
         <v>1.317400000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>2.908799999999999</v>
+        <v>2.9088</v>
       </c>
       <c r="O28" t="n">
         <v>-1.5913</v>
@@ -2638,13 +2638,13 @@
         <v>18.4999</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.3753</v>
+        <v>-0.7107999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.3735999999999998</v>
+        <v>-0.3734999999999998</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.0014</v>
+        <v>-0.3371</v>
       </c>
       <c r="V28" t="n">
         <v>5.898999999999999</v>
